--- a/dataset/v2/equipment_progress.xlsx
+++ b/dataset/v2/equipment_progress.xlsx
@@ -544,12 +544,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STA-CMP-1525</t>
+          <t>STA-DRY-1521</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PK-2401</t>
+          <t>TK-2101</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Load test, compressor package PK-2401</t>
+          <t>Water fill and settlement check, TK-2101</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -567,32 +567,37 @@
           <t>STA</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Substation</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>05/Oct/2026</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>940</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>940</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STA-FLR-1221</t>
+          <t>STA-DRY-1522</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FST-1301</t>
+          <t>TK-2102</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -602,7 +607,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erect flare stack FST-1301, guys tensioned</t>
+          <t>Water fill and calibration strapping, TK-2102</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -612,35 +617,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1010</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STA-FLR-1222</t>
+          <t>STA-FLR-1220</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>V-1401</t>
+          <t>FST-1301</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Set flare knockout drum V-1401</t>
+          <t>Shop assemble flare stack sections, FST-1301</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -670,20 +670,20 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23/Apr/2026</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STA-FLR-1224</t>
+          <t>STA-FLR-1221</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Install flare tip ignition panel and pilot lines</t>
+          <t>Erect flare stack FST-1301, guys tensioned</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/May/2026</t>
+          <t>30/Apr/2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -731,12 +731,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STA-FLS-1526</t>
+          <t>STA-FLR-1222</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FST-1301</t>
+          <t>V-1401</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Flare pilot ignition and pilot line purge test</t>
+          <t>Set flare knockout drum V-1401</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -754,19 +754,9 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Substation</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>05/11/2026</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>05/Nov/2026</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -779,12 +769,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STA-INT-1214</t>
+          <t>STA-FLR-1223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V-2201</t>
+          <t>FST-1301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -794,7 +784,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fit internals and demisters, V-2201</t>
+          <t>Install flare tip and molecular seal, FST-1301</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -804,17 +794,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Substation</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>04/May/2026</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>05/May/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -827,12 +817,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STA-MCH-1216</t>
+          <t>STA-FLS-1526</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PK-2401</t>
+          <t>FST-1301</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -842,7 +832,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Set instrument air compressors, package PK-2401</t>
+          <t>Flare pilot ignition and pilot line purge test</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -852,17 +842,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -875,12 +865,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STA-MCH-1217</t>
+          <t>STA-INT-1213</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PK-2401</t>
+          <t>V-2101</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alignment check and coupling, compressor PK-2401 to receiver</t>
+          <t>Load and fit internals and demisters, V-2101</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -900,17 +890,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>19/May/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -946,9 +936,9 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -991,12 +981,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1014,7 +1004,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STA-ROT-1523</t>
+          <t>STA-MCH-1242</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1029,7 +1019,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Motor bump test, pumps P-1401A/B</t>
+          <t>Motor mounting and bolt torque, P-1401A/B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1044,12 +1034,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24/09/2026</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1062,12 +1052,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STA-ROT-1524</t>
+          <t>STA-MS-1556</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P-1401A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1077,7 +1067,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Performance run, crude transfer pumps P-1401A/B</t>
+          <t>First crude transfer to TK-2101</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1085,37 +1075,26 @@
           <t>STA</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>22/Feb/2027</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
+          <t>2027-02-22</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STA-RUN-1527</t>
+          <t>STA-PRS-1520</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V-1101</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1125,7 +1104,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>72-hour integrated reliability run, process train</t>
+          <t>Tightness and pressure test, separators V-1101 and V-1201</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1135,35 +1114,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/Jan/2027</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>08/01/2027</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STA-SET-1203</t>
+          <t>STA-ROT-1524</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>V-1201</t>
+          <t>P-1401A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1173,7 +1152,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rig and set glycol contactor V-1201</t>
+          <t>Performance run, crude transfer pumps P-1401A/B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1183,35 +1162,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Tank Farm</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15/Jun/2026</t>
+          <t>28/Sep/2026</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STA-SET-1204</t>
+          <t>STA-SET-1200</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V-1101</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1221,7 +1200,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Set production manifold header assemblies, Unit 1, 16"-P-1002-A1A tie-</t>
+          <t>Receive and stage separator V-1101, transport from laydown</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1231,35 +1210,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tank Farm</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/May/2026</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>09/May/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STA-SET-1207</t>
+          <t>STA-SET-1202</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V-1101</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1269,7 +1248,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Set fuel gas skid, utilities plinth U1</t>
+          <t>Plumb, alignment and bolt torque, V-1101</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1277,9 +1256,19 @@
           <t>STA</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15/Jun/2026</t>
+          <t>11/Jun/2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1292,12 +1281,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STA-SET-1211</t>
+          <t>STA-SET-1203</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>V-2201</t>
+          <t>V-1201</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1307,7 +1296,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Set test separator V-2201, Unit 2</t>
+          <t>Rig and set glycol contactor V-1201</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1317,17 +1306,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>30/Apr/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1340,12 +1329,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STA-SET-1212</t>
+          <t>STA-SET-1204</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WHCP-2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1355,7 +1344,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Set wellhead control panel skid WHCP-2101, Unit 2</t>
+          <t>Set production manifold header assemblies, Unit 1, 16"-P-1002-A1A tie-</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1363,32 +1352,37 @@
           <t>STA</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Substation</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>23/Apr/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STA-SET-1243</t>
+          <t>STA-SET-1207</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CS-2501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1398,7 +1392,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Set chemical injection skids CS-2501 and CS-2502, wellhead U1/U2</t>
+          <t>Set fuel gas skid, utilities plinth U1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1408,35 +1402,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manifold</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>15/Jun/2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STA-SET-1244</t>
+          <t>STA-SET-1211</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V-2201</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1446,7 +1440,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Monorail and davit erection, separator platforms</t>
+          <t>Set test separator V-2201, Unit 2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1456,17 +1450,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Substation</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>30/Apr/2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>16/Jun/2026</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1479,12 +1473,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STA-TNK-1230</t>
+          <t>STA-SET-1244</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TK-2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1494,7 +1488,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tank shell erection, courses 1-3, TK-2101</t>
+          <t>Monorail and davit erection, separator platforms</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1504,30 +1498,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STA-TNK-1232</t>
+          <t>STA-TNK-1230</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1537,12 +1531,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>L6</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shell course 3 and wind girder, TK-2101</t>
+          <t>Tank shell erection, courses 1-3, TK-2101</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1552,30 +1546,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>31/May/2026</t>
+          <t>Manifold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="J26" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STA-TNK-1233</t>
+          <t>STA-TNK-1231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1585,12 +1574,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>L5</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tank roof structure and fittings, TK-2101</t>
+          <t>Shell courses 1-2, tank TK-2101</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1600,24 +1589,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/Jun/2026</t>
+          <t>25/May/2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -1691,12 +1680,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
+          <t>Manifold</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1732,14 +1721,19 @@
           <t>STA</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tank Farm</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>08/May/2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>11/May/2026</t>
         </is>
       </c>
       <c r="I30" t="n">
